--- a/outputs/Block5_Control_Summary.xlsx
+++ b/outputs/Block5_Control_Summary.xlsx
@@ -435,22 +435,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -458,22 +458,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C3">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
   </sheetData>
